--- a/JsonConverter/ExcelFiles/Entity.xlsx
+++ b/JsonConverter/ExcelFiles/Entity.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\MinHyeong2DProject\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\Fantastic4\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86166028-B2C1-49D3-A752-71E894D51953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C4BA14-5916-4AB8-B8EB-64AEF4AC2C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="54">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -93,10 +93,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Enum</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>enemy_03</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -133,10 +129,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>tower_06</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>화살 원시인</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -145,10 +137,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>밧줄 원시인</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>enemy_04</t>
   </si>
   <si>
@@ -187,37 +175,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Sprite/Icon/tower_01_icon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprite/Icon/tower_02_icon</t>
-  </si>
-  <si>
-    <t>Assets/Sprite/Icon/ChickenIcon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Sprite/Icon/Pig</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprite/Icon/tower_03_icon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprite/Icon/tower_04_icon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprite/Icon/tower_05_icon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sprite/Icon/tower_06_icon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>창을 이용해 적을 찌르는 원시인&lt;br&gt;날아다니는 유닛을 공격할 수 없습니다.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -238,7 +195,43 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>밧줄을 던져 적의 이동속도를 감소시키는 원시인&lt;br&gt;지상과 공중 유닛을 공격할 수 있습니다.</t>
+    <t>Sprite/Icon/Enemy_02_icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/Enemy_03_icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/Enemy_04_icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/Enemy_05_icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/Enemy_01_icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/Tower_05_icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/Tower_04_icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/Tower_03_icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/Tower_01_Icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprite/Icon/Tower_02_Icon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -699,10 +692,10 @@
         <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="8"/>
@@ -719,13 +712,13 @@
         <v>5</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
@@ -742,13 +735,13 @@
         <v>7</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="8"/>
@@ -766,16 +759,16 @@
         <v>14</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
@@ -790,19 +783,19 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
@@ -817,19 +810,19 @@
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="A7" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
@@ -844,19 +837,19 @@
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -870,20 +863,20 @@
       <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A9" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>55</v>
+      <c r="A9" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
@@ -898,13 +891,13 @@
     </row>
     <row r="10" spans="1:15" ht="15.75" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>8</v>
+        <v>16</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>9</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>17</v>
@@ -924,14 +917,14 @@
       <c r="O10" s="3"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A11" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>38</v>
+      <c r="A11" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>19</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>17</v>
@@ -952,19 +945,19 @@
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1">
       <c r="A12" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>37</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
@@ -979,19 +972,19 @@
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1">
       <c r="A13" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>40</v>
+        <v>30</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>38</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
@@ -1005,21 +998,6 @@
       <c r="O13" s="3"/>
     </row>
     <row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A14" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>44</v>
-      </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
